--- a/Raw data standard Title/GANTER 原始记录文件表头.xlsx
+++ b/Raw data standard Title/GANTER 原始记录文件表头.xlsx
@@ -188,7 +188,7 @@
     <t>AOU/VOL/#4</t>
   </si>
   <si>
-    <t>[ ｰC]</t>
+    <t>[ °C]</t>
   </si>
   <si>
     <t>[mbar]</t>
